--- a/DETALLE FACTURAS COMBUSTIBLES ENERO A ABRIL 24-2026.xlsx
+++ b/DETALLE FACTURAS COMBUSTIBLES ENERO A ABRIL 24-2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://todomar-my.sharepoint.com/personal/cartera_todomar_com/Documents/Escritorio/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\Inteligencia Artificial\Productividad\Gasolina\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD1F1A46-1388-4352-8921-6AA1DF31A5C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC0A45FD-F568-4148-BFDC-7A9C4440B731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{498B3117-BC09-44C4-A1EF-62B489AD5F6D}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{498B3117-BC09-44C4-A1EF-62B489AD5F6D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$J$115</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="21">
   <si>
     <t>CUENTA</t>
   </si>
@@ -88,12 +88,40 @@
   <si>
     <t>FC</t>
   </si>
+  <si>
+    <t>Nombre de Bote</t>
+  </si>
+  <si>
+    <t>Fecha y hora de tanqueo</t>
+  </si>
+  <si>
+    <t>Conciliacion</t>
+  </si>
+  <si>
+    <t>Estado: OK ( el Valor de la remision es el mismo de la factura ) - No hay remision(Si no hay remision en el zip) - Remision con valor diferente( el valor de remision no conincide con el valor facturado)</t>
+  </si>
+  <si>
+    <t>Valor</t>
+  </si>
+  <si>
+    <t>Diferencia encontrada e n la conciliacion</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -119,14 +147,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -459,22 +493,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21F4A740-06A0-4D72-BF7F-E5C1A1E0BADC}">
-  <dimension ref="A1:J115"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O115"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.88671875" customWidth="1"/>
+    <col min="12" max="12" width="20.77734375" customWidth="1"/>
+    <col min="13" max="13" width="21.88671875" customWidth="1"/>
+    <col min="14" max="14" width="29.109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -499,14 +537,26 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="O1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>13050550</v>
       </c>
@@ -531,14 +581,20 @@
       <c r="H2" t="s">
         <v>11</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="3">
         <v>641940</v>
       </c>
       <c r="J2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="N2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>13050550</v>
       </c>
@@ -563,14 +619,14 @@
       <c r="H3" t="s">
         <v>11</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="3">
         <v>685948.32</v>
       </c>
       <c r="J3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>13050550</v>
       </c>
@@ -595,14 +651,14 @@
       <c r="H4" t="s">
         <v>11</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="3">
         <v>745200</v>
       </c>
       <c r="J4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>13050550</v>
       </c>
@@ -627,14 +683,14 @@
       <c r="H5" t="s">
         <v>11</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="3">
         <v>546794.64</v>
       </c>
       <c r="J5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>13050550</v>
       </c>
@@ -659,14 +715,14 @@
       <c r="H6" t="s">
         <v>11</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="3">
         <v>548218.80000000005</v>
       </c>
       <c r="J6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>13050550</v>
       </c>
@@ -691,14 +747,14 @@
       <c r="H7" t="s">
         <v>11</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="3">
         <v>530118.72</v>
       </c>
       <c r="J7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>13050550</v>
       </c>
@@ -723,14 +779,14 @@
       <c r="H8" t="s">
         <v>11</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="3">
         <v>695354.4</v>
       </c>
       <c r="J8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>13050550</v>
       </c>
@@ -755,14 +811,14 @@
       <c r="H9" t="s">
         <v>11</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="3">
         <v>579600</v>
       </c>
       <c r="J9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>13050550</v>
       </c>
@@ -787,14 +843,14 @@
       <c r="H10" t="s">
         <v>11</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="3">
         <v>529920</v>
       </c>
       <c r="J10" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>13050550</v>
       </c>
@@ -819,14 +875,14 @@
       <c r="H11" t="s">
         <v>11</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="3">
         <v>861136.56</v>
       </c>
       <c r="J11" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>13050550</v>
       </c>
@@ -851,14 +907,14 @@
       <c r="H12" t="s">
         <v>11</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="3">
         <v>579600</v>
       </c>
       <c r="J12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>13050550</v>
       </c>
@@ -883,14 +939,14 @@
       <c r="H13" t="s">
         <v>11</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="3">
         <v>529920</v>
       </c>
       <c r="J13" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13050550</v>
       </c>
@@ -915,14 +971,14 @@
       <c r="H14" t="s">
         <v>11</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="3">
         <v>579252.24</v>
       </c>
       <c r="J14" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13050550</v>
       </c>
@@ -947,14 +1003,14 @@
       <c r="H15" t="s">
         <v>11</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="3">
         <v>745448.4</v>
       </c>
       <c r="J15" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>13050550</v>
       </c>
@@ -979,14 +1035,14 @@
       <c r="H16" t="s">
         <v>11</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="3">
         <v>745200</v>
       </c>
       <c r="J16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>13050550</v>
       </c>
@@ -1011,14 +1067,14 @@
       <c r="H17" t="s">
         <v>11</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="3">
         <v>529936.56000000006</v>
       </c>
       <c r="J17" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>13050550</v>
       </c>
@@ -1043,14 +1099,14 @@
       <c r="H18" t="s">
         <v>11</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="3">
         <v>529920</v>
       </c>
       <c r="J18" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>13050550</v>
       </c>
@@ -1075,14 +1131,14 @@
       <c r="H19" t="s">
         <v>11</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="3">
         <v>529920</v>
       </c>
       <c r="J19" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>13050550</v>
       </c>
@@ -1107,14 +1163,14 @@
       <c r="H20" t="s">
         <v>11</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="3">
         <v>579600</v>
       </c>
       <c r="J20" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>13050550</v>
       </c>
@@ -1139,14 +1195,14 @@
       <c r="H21" t="s">
         <v>11</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="3">
         <v>745200</v>
       </c>
       <c r="J21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>13050550</v>
       </c>
@@ -1171,14 +1227,14 @@
       <c r="H22" t="s">
         <v>11</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="3">
         <v>579600</v>
       </c>
       <c r="J22" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>13050550</v>
       </c>
@@ -1203,14 +1259,14 @@
       <c r="H23" t="s">
         <v>11</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="3">
         <v>746988.48</v>
       </c>
       <c r="J23" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>13050550</v>
       </c>
@@ -1235,14 +1291,14 @@
       <c r="H24" t="s">
         <v>11</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="3">
         <v>662400</v>
       </c>
       <c r="J24" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>13050550</v>
       </c>
@@ -1267,14 +1323,14 @@
       <c r="H25" t="s">
         <v>11</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="3">
         <v>662400</v>
       </c>
       <c r="J25" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>13050550</v>
       </c>
@@ -1299,14 +1355,14 @@
       <c r="H26" t="s">
         <v>11</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="3">
         <v>794880</v>
       </c>
       <c r="J26" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>13050550</v>
       </c>
@@ -1331,14 +1387,14 @@
       <c r="H27" t="s">
         <v>11</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="3">
         <v>563040</v>
       </c>
       <c r="J27" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>13050550</v>
       </c>
@@ -1363,14 +1419,14 @@
       <c r="H28" t="s">
         <v>11</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="3">
         <v>526711.92000000004</v>
       </c>
       <c r="J28" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>13050550</v>
       </c>
@@ -1395,14 +1451,14 @@
       <c r="H29" t="s">
         <v>11</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="3">
         <v>558600</v>
       </c>
       <c r="J29" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>13050550</v>
       </c>
@@ -1427,14 +1483,14 @@
       <c r="H30" t="s">
         <v>11</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="3">
         <v>574560</v>
       </c>
       <c r="J30" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>13050550</v>
       </c>
@@ -1459,14 +1515,14 @@
       <c r="H31" t="s">
         <v>11</v>
       </c>
-      <c r="I31">
+      <c r="I31" s="3">
         <v>558600</v>
       </c>
       <c r="J31" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>13050550</v>
       </c>
@@ -1491,14 +1547,14 @@
       <c r="H32" t="s">
         <v>11</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="3">
         <v>558600</v>
       </c>
       <c r="J32" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>13050550</v>
       </c>
@@ -1523,14 +1579,14 @@
       <c r="H33" t="s">
         <v>11</v>
       </c>
-      <c r="I33">
+      <c r="I33" s="3">
         <v>590520</v>
       </c>
       <c r="J33" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>13050550</v>
       </c>
@@ -1555,14 +1611,14 @@
       <c r="H34" t="s">
         <v>11</v>
       </c>
-      <c r="I34">
+      <c r="I34" s="3">
         <v>622440</v>
       </c>
       <c r="J34" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>13050550</v>
       </c>
@@ -1587,14 +1643,14 @@
       <c r="H35" t="s">
         <v>11</v>
       </c>
-      <c r="I35">
+      <c r="I35" s="3">
         <v>686280</v>
       </c>
       <c r="J35" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>13050550</v>
       </c>
@@ -1619,14 +1675,14 @@
       <c r="H36" t="s">
         <v>11</v>
       </c>
-      <c r="I36">
+      <c r="I36" s="3">
         <v>686280</v>
       </c>
       <c r="J36" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>13050550</v>
       </c>
@@ -1651,14 +1707,14 @@
       <c r="H37" t="s">
         <v>11</v>
       </c>
-      <c r="I37">
+      <c r="I37" s="3">
         <v>750120</v>
       </c>
       <c r="J37" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>13050550</v>
       </c>
@@ -1683,14 +1739,14 @@
       <c r="H38" t="s">
         <v>11</v>
       </c>
-      <c r="I38">
+      <c r="I38" s="3">
         <v>558600</v>
       </c>
       <c r="J38" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>13050550</v>
       </c>
@@ -1715,14 +1771,14 @@
       <c r="H39" t="s">
         <v>11</v>
       </c>
-      <c r="I39">
+      <c r="I39" s="3">
         <v>638400</v>
       </c>
       <c r="J39" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>13050550</v>
       </c>
@@ -1747,14 +1803,14 @@
       <c r="H40" t="s">
         <v>11</v>
       </c>
-      <c r="I40">
+      <c r="I40" s="3">
         <v>702240</v>
       </c>
       <c r="J40" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>13050550</v>
       </c>
@@ -1779,14 +1835,14 @@
       <c r="H41" t="s">
         <v>11</v>
       </c>
-      <c r="I41">
+      <c r="I41" s="3">
         <v>558600</v>
       </c>
       <c r="J41" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>13050550</v>
       </c>
@@ -1811,14 +1867,14 @@
       <c r="H42" t="s">
         <v>11</v>
       </c>
-      <c r="I42">
+      <c r="I42" s="3">
         <v>606480</v>
       </c>
       <c r="J42" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>13050550</v>
       </c>
@@ -1843,14 +1899,14 @@
       <c r="H43" t="s">
         <v>11</v>
       </c>
-      <c r="I43">
+      <c r="I43" s="3">
         <v>718200</v>
       </c>
       <c r="J43" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>13050550</v>
       </c>
@@ -1875,14 +1931,14 @@
       <c r="H44" t="s">
         <v>11</v>
       </c>
-      <c r="I44">
+      <c r="I44" s="3">
         <v>558600</v>
       </c>
       <c r="J44" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>13050550</v>
       </c>
@@ -1907,14 +1963,14 @@
       <c r="H45" t="s">
         <v>11</v>
       </c>
-      <c r="I45">
+      <c r="I45" s="3">
         <v>718200</v>
       </c>
       <c r="J45" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>13050550</v>
       </c>
@@ -1939,14 +1995,14 @@
       <c r="H46" t="s">
         <v>11</v>
       </c>
-      <c r="I46">
+      <c r="I46" s="3">
         <v>446880</v>
       </c>
       <c r="J46" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>13050550</v>
       </c>
@@ -1971,14 +2027,14 @@
       <c r="H47" t="s">
         <v>11</v>
       </c>
-      <c r="I47">
+      <c r="I47" s="3">
         <v>558600</v>
       </c>
       <c r="J47" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>13050550</v>
       </c>
@@ -2003,14 +2059,14 @@
       <c r="H48" t="s">
         <v>11</v>
       </c>
-      <c r="I48">
+      <c r="I48" s="3">
         <v>861840</v>
       </c>
       <c r="J48" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>13050550</v>
       </c>
@@ -2035,14 +2091,14 @@
       <c r="H49" t="s">
         <v>11</v>
       </c>
-      <c r="I49">
+      <c r="I49" s="3">
         <v>541100</v>
       </c>
       <c r="J49" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>13050550</v>
       </c>
@@ -2067,14 +2123,14 @@
       <c r="H50" t="s">
         <v>11</v>
       </c>
-      <c r="I50">
+      <c r="I50" s="3">
         <v>463800</v>
       </c>
       <c r="J50" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>13050550</v>
       </c>
@@ -2099,14 +2155,14 @@
       <c r="H51" t="s">
         <v>11</v>
       </c>
-      <c r="I51">
+      <c r="I51" s="3">
         <v>525640</v>
       </c>
       <c r="J51" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>13050550</v>
       </c>
@@ -2131,14 +2187,14 @@
       <c r="H52" t="s">
         <v>11</v>
       </c>
-      <c r="I52">
+      <c r="I52" s="3">
         <v>525640</v>
       </c>
       <c r="J52" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>13050550</v>
       </c>
@@ -2163,14 +2219,14 @@
       <c r="H53" t="s">
         <v>11</v>
       </c>
-      <c r="I53">
+      <c r="I53" s="3">
         <v>680240</v>
       </c>
       <c r="J53" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>13050550</v>
       </c>
@@ -2195,14 +2251,14 @@
       <c r="H54" t="s">
         <v>11</v>
       </c>
-      <c r="I54">
+      <c r="I54" s="3">
         <v>850300</v>
       </c>
       <c r="J54" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>13050550</v>
       </c>
@@ -2227,14 +2283,14 @@
       <c r="H55" t="s">
         <v>11</v>
       </c>
-      <c r="I55">
+      <c r="I55" s="3">
         <v>510180</v>
       </c>
       <c r="J55" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>13050550</v>
       </c>
@@ -2259,14 +2315,14 @@
       <c r="H56" t="s">
         <v>11</v>
       </c>
-      <c r="I56">
+      <c r="I56" s="3">
         <v>850300</v>
       </c>
       <c r="J56" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>13050550</v>
       </c>
@@ -2291,14 +2347,14 @@
       <c r="H57" t="s">
         <v>11</v>
       </c>
-      <c r="I57">
+      <c r="I57" s="3">
         <v>803920</v>
       </c>
       <c r="J57" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>13050550</v>
       </c>
@@ -2323,14 +2379,14 @@
       <c r="H58" t="s">
         <v>11</v>
       </c>
-      <c r="I58">
+      <c r="I58" s="3">
         <v>819380</v>
       </c>
       <c r="J58" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>13050550</v>
       </c>
@@ -2355,14 +2411,14 @@
       <c r="H59" t="s">
         <v>11</v>
       </c>
-      <c r="I59">
+      <c r="I59" s="3">
         <v>742080</v>
       </c>
       <c r="J59" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>13050550</v>
       </c>
@@ -2387,14 +2443,14 @@
       <c r="H60" t="s">
         <v>11</v>
       </c>
-      <c r="I60">
+      <c r="I60" s="3">
         <v>1082200</v>
       </c>
       <c r="J60" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>13050550</v>
       </c>
@@ -2419,14 +2475,14 @@
       <c r="H61" t="s">
         <v>11</v>
       </c>
-      <c r="I61">
+      <c r="I61" s="3">
         <v>958520</v>
       </c>
       <c r="J61" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>13050550</v>
       </c>
@@ -2451,14 +2507,14 @@
       <c r="H62" t="s">
         <v>11</v>
       </c>
-      <c r="I62">
+      <c r="I62" s="3">
         <v>927600</v>
       </c>
       <c r="J62" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>13050550</v>
       </c>
@@ -2483,14 +2539,14 @@
       <c r="H63" t="s">
         <v>11</v>
       </c>
-      <c r="I63">
+      <c r="I63" s="3">
         <v>819380</v>
       </c>
       <c r="J63" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>13050550</v>
       </c>
@@ -2515,14 +2571,14 @@
       <c r="H64" t="s">
         <v>11</v>
       </c>
-      <c r="I64">
+      <c r="I64" s="3">
         <v>587480</v>
       </c>
       <c r="J64" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>13050550</v>
       </c>
@@ -2547,14 +2603,14 @@
       <c r="H65" t="s">
         <v>11</v>
       </c>
-      <c r="I65">
+      <c r="I65" s="3">
         <v>649320</v>
       </c>
       <c r="J65" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>13050550</v>
       </c>
@@ -2579,14 +2635,14 @@
       <c r="H66" t="s">
         <v>11</v>
       </c>
-      <c r="I66">
+      <c r="I66" s="3">
         <v>664780</v>
       </c>
       <c r="J66" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>13050550</v>
       </c>
@@ -2611,14 +2667,14 @@
       <c r="H67" t="s">
         <v>11</v>
       </c>
-      <c r="I67">
+      <c r="I67" s="3">
         <v>773000</v>
       </c>
       <c r="J67" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>13050550</v>
       </c>
@@ -2643,14 +2699,14 @@
       <c r="H68" t="s">
         <v>11</v>
       </c>
-      <c r="I68">
+      <c r="I68" s="3">
         <v>742080</v>
       </c>
       <c r="J68" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>13050550</v>
       </c>
@@ -2675,14 +2731,14 @@
       <c r="H69" t="s">
         <v>11</v>
       </c>
-      <c r="I69">
+      <c r="I69" s="3">
         <v>67199.990000000005</v>
       </c>
       <c r="J69" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>13050550</v>
       </c>
@@ -2707,14 +2763,14 @@
       <c r="H70" t="s">
         <v>11</v>
       </c>
-      <c r="I70">
+      <c r="I70" s="3">
         <v>1236800</v>
       </c>
       <c r="J70" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>13050550</v>
       </c>
@@ -2739,14 +2795,14 @@
       <c r="H71" t="s">
         <v>11</v>
       </c>
-      <c r="I71">
+      <c r="I71" s="3">
         <v>649320</v>
       </c>
       <c r="J71" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>13050550</v>
       </c>
@@ -2771,14 +2827,14 @@
       <c r="H72" t="s">
         <v>11</v>
       </c>
-      <c r="I72">
+      <c r="I72" s="3">
         <v>541100</v>
       </c>
       <c r="J72" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>13050550</v>
       </c>
@@ -2803,14 +2859,14 @@
       <c r="H73" t="s">
         <v>11</v>
       </c>
-      <c r="I73">
+      <c r="I73" s="3">
         <v>649320</v>
       </c>
       <c r="J73" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>13050550</v>
       </c>
@@ -2835,14 +2891,14 @@
       <c r="H74" t="s">
         <v>11</v>
       </c>
-      <c r="I74">
+      <c r="I74" s="3">
         <v>541100</v>
       </c>
       <c r="J74" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>13050550</v>
       </c>
@@ -2867,14 +2923,14 @@
       <c r="H75" t="s">
         <v>11</v>
       </c>
-      <c r="I75">
+      <c r="I75" s="3">
         <v>633860</v>
       </c>
       <c r="J75" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>13050550</v>
       </c>
@@ -2899,14 +2955,14 @@
       <c r="H76" t="s">
         <v>11</v>
       </c>
-      <c r="I76">
+      <c r="I76" s="3">
         <v>556150</v>
       </c>
       <c r="J76" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>13050550</v>
       </c>
@@ -2931,14 +2987,14 @@
       <c r="H77" t="s">
         <v>11</v>
       </c>
-      <c r="I77">
+      <c r="I77" s="3">
         <v>715050</v>
       </c>
       <c r="J77" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>13050550</v>
       </c>
@@ -2963,14 +3019,14 @@
       <c r="H78" t="s">
         <v>11</v>
       </c>
-      <c r="I78">
+      <c r="I78" s="3">
         <v>556150</v>
       </c>
       <c r="J78" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>13050550</v>
       </c>
@@ -2995,14 +3051,14 @@
       <c r="H79" t="s">
         <v>11</v>
       </c>
-      <c r="I79">
+      <c r="I79" s="3">
         <v>667380</v>
       </c>
       <c r="J79" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>13050550</v>
       </c>
@@ -3027,14 +3083,14 @@
       <c r="H80" t="s">
         <v>11</v>
       </c>
-      <c r="I80">
+      <c r="I80" s="3">
         <v>492590</v>
       </c>
       <c r="J80" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>13050550</v>
       </c>
@@ -3059,14 +3115,14 @@
       <c r="H81" t="s">
         <v>11</v>
       </c>
-      <c r="I81">
+      <c r="I81" s="3">
         <v>603820</v>
       </c>
       <c r="J81" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>13050550</v>
       </c>
@@ -3091,14 +3147,14 @@
       <c r="H82" t="s">
         <v>11</v>
       </c>
-      <c r="I82">
+      <c r="I82" s="3">
         <v>842170</v>
       </c>
       <c r="J82" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>13050550</v>
       </c>
@@ -3123,14 +3179,14 @@
       <c r="H83" t="s">
         <v>11</v>
       </c>
-      <c r="I83">
+      <c r="I83" s="3">
         <v>270130</v>
       </c>
       <c r="J83" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>13050550</v>
       </c>
@@ -3155,14 +3211,14 @@
       <c r="H84" t="s">
         <v>11</v>
       </c>
-      <c r="I84">
+      <c r="I84" s="3">
         <v>556150</v>
       </c>
       <c r="J84" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>13050550</v>
       </c>
@@ -3187,14 +3243,14 @@
       <c r="H85" t="s">
         <v>11</v>
       </c>
-      <c r="I85">
+      <c r="I85" s="3">
         <v>476700</v>
       </c>
       <c r="J85" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>13050550</v>
       </c>
@@ -3219,14 +3275,14 @@
       <c r="H86" t="s">
         <v>11</v>
       </c>
-      <c r="I86">
+      <c r="I86" s="3">
         <v>683270</v>
       </c>
       <c r="J86" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>13050550</v>
       </c>
@@ -3251,14 +3307,14 @@
       <c r="H87" t="s">
         <v>11</v>
       </c>
-      <c r="I87">
+      <c r="I87" s="3">
         <v>794500</v>
       </c>
       <c r="J87" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>13050550</v>
       </c>
@@ -3283,14 +3339,14 @@
       <c r="H88" t="s">
         <v>11</v>
       </c>
-      <c r="I88">
+      <c r="I88" s="3">
         <v>365470</v>
       </c>
       <c r="J88" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>13050550</v>
       </c>
@@ -3315,14 +3371,14 @@
       <c r="H89" t="s">
         <v>11</v>
       </c>
-      <c r="I89">
+      <c r="I89" s="3">
         <v>95943.82</v>
       </c>
       <c r="J89" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>13050550</v>
       </c>
@@ -3347,14 +3403,14 @@
       <c r="H90" t="s">
         <v>11</v>
       </c>
-      <c r="I90">
+      <c r="I90" s="3">
         <v>476700</v>
       </c>
       <c r="J90" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>13050550</v>
       </c>
@@ -3379,14 +3435,14 @@
       <c r="H91" t="s">
         <v>11</v>
       </c>
-      <c r="I91">
+      <c r="I91" s="3">
         <v>365470</v>
       </c>
       <c r="J91" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>13050550</v>
       </c>
@@ -3411,14 +3467,14 @@
       <c r="H92" t="s">
         <v>11</v>
       </c>
-      <c r="I92">
+      <c r="I92" s="3">
         <v>508480</v>
       </c>
       <c r="J92" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>13050550</v>
       </c>
@@ -3443,14 +3499,14 @@
       <c r="H93" t="s">
         <v>11</v>
       </c>
-      <c r="I93">
+      <c r="I93" s="3">
         <v>556150</v>
       </c>
       <c r="J93" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>13050550</v>
       </c>
@@ -3475,14 +3531,14 @@
       <c r="H94" t="s">
         <v>11</v>
       </c>
-      <c r="I94">
+      <c r="I94" s="3">
         <v>476700</v>
       </c>
       <c r="J94" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>13050550</v>
       </c>
@@ -3507,14 +3563,14 @@
       <c r="H95" t="s">
         <v>11</v>
       </c>
-      <c r="I95">
+      <c r="I95" s="3">
         <v>715050</v>
       </c>
       <c r="J95" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>13050550</v>
       </c>
@@ -3539,14 +3595,14 @@
       <c r="H96" t="s">
         <v>11</v>
       </c>
-      <c r="I96">
+      <c r="I96" s="3">
         <v>476700</v>
       </c>
       <c r="J96" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>13050550</v>
       </c>
@@ -3571,14 +3627,14 @@
       <c r="H97" t="s">
         <v>11</v>
       </c>
-      <c r="I97">
+      <c r="I97" s="3">
         <v>873950</v>
       </c>
       <c r="J97" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>13050550</v>
       </c>
@@ -3603,14 +3659,14 @@
       <c r="H98" t="s">
         <v>11</v>
       </c>
-      <c r="I98">
+      <c r="I98" s="3">
         <v>842170</v>
       </c>
       <c r="J98" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>13050550</v>
       </c>
@@ -3635,14 +3691,14 @@
       <c r="H99" t="s">
         <v>11</v>
       </c>
-      <c r="I99">
+      <c r="I99" s="3">
         <v>463800</v>
       </c>
       <c r="J99" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>13050550</v>
       </c>
@@ -3667,14 +3723,14 @@
       <c r="H100" t="s">
         <v>11</v>
       </c>
-      <c r="I100">
+      <c r="I100" s="3">
         <v>794547.67</v>
       </c>
       <c r="J100" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>13050550</v>
       </c>
@@ -3699,14 +3755,14 @@
       <c r="H101" t="s">
         <v>11</v>
       </c>
-      <c r="I101">
+      <c r="I101" s="3">
         <v>556150</v>
       </c>
       <c r="J101" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>13050550</v>
       </c>
@@ -3731,14 +3787,14 @@
       <c r="H102" t="s">
         <v>11</v>
       </c>
-      <c r="I102">
+      <c r="I102" s="3">
         <v>508480</v>
       </c>
       <c r="J102" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>13050550</v>
       </c>
@@ -3763,14 +3819,14 @@
       <c r="H103" t="s">
         <v>11</v>
       </c>
-      <c r="I103">
+      <c r="I103" s="3">
         <v>699160</v>
       </c>
       <c r="J103" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>13050550</v>
       </c>
@@ -3795,14 +3851,14 @@
       <c r="H104" t="s">
         <v>11</v>
       </c>
-      <c r="I104">
+      <c r="I104" s="3">
         <v>651490</v>
       </c>
       <c r="J104" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>13050550</v>
       </c>
@@ -3827,14 +3883,14 @@
       <c r="H105" t="s">
         <v>11</v>
       </c>
-      <c r="I105">
+      <c r="I105" s="3">
         <v>429030</v>
       </c>
       <c r="J105" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>13050550</v>
       </c>
@@ -3859,14 +3915,14 @@
       <c r="H106" t="s">
         <v>11</v>
       </c>
-      <c r="I106">
+      <c r="I106" s="3">
         <v>492590</v>
       </c>
       <c r="J106" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>13050550</v>
       </c>
@@ -3891,14 +3947,14 @@
       <c r="H107" t="s">
         <v>11</v>
       </c>
-      <c r="I107">
+      <c r="I107" s="3">
         <v>397250</v>
       </c>
       <c r="J107" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>13050550</v>
       </c>
@@ -3923,14 +3979,14 @@
       <c r="H108" t="s">
         <v>11</v>
       </c>
-      <c r="I108">
+      <c r="I108" s="3">
         <v>651490</v>
       </c>
       <c r="J108" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>13050550</v>
       </c>
@@ -3955,14 +4011,14 @@
       <c r="H109" t="s">
         <v>11</v>
       </c>
-      <c r="I109">
+      <c r="I109" s="3">
         <v>556150</v>
       </c>
       <c r="J109" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>13050550</v>
       </c>
@@ -3987,14 +4043,14 @@
       <c r="H110" t="s">
         <v>11</v>
       </c>
-      <c r="I110">
+      <c r="I110" s="3">
         <v>444920</v>
       </c>
       <c r="J110" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>13050550</v>
       </c>
@@ -4019,14 +4075,14 @@
       <c r="H111" t="s">
         <v>11</v>
       </c>
-      <c r="I111">
+      <c r="I111" s="3">
         <v>508480</v>
       </c>
       <c r="J111" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>13050550</v>
       </c>
@@ -4051,14 +4107,14 @@
       <c r="H112" t="s">
         <v>11</v>
       </c>
-      <c r="I112">
+      <c r="I112" s="3">
         <v>143010</v>
       </c>
       <c r="J112" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>13050550</v>
       </c>
@@ -4083,14 +4139,14 @@
       <c r="H113" t="s">
         <v>11</v>
       </c>
-      <c r="I113">
+      <c r="I113" s="3">
         <v>556150</v>
       </c>
       <c r="J113" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>13050550</v>
       </c>
@@ -4115,14 +4171,14 @@
       <c r="H114" t="s">
         <v>11</v>
       </c>
-      <c r="I114">
+      <c r="I114" s="3">
         <v>794500</v>
       </c>
       <c r="J114" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>13050550</v>
       </c>
@@ -4147,7 +4203,7 @@
       <c r="H115" t="s">
         <v>11</v>
       </c>
-      <c r="I115">
+      <c r="I115" s="3">
         <v>556150</v>
       </c>
       <c r="J115" t="s">
